--- a/Reports/03_الإصلاحات_والتصحيحات/المطابقات_البنكية/سجل_قيود_التسوية_SLX.xlsx
+++ b/Reports/03_الإصلاحات_والتصحيحات/المطابقات_البنكية/سجل_قيود_التسوية_SLX.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +41,12 @@
     <font>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +71,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00fdeeee"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00d9ead3"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -132,6 +141,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -499,17 +520,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,7 +542,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>إعداد: التدقيق الداخلي (Solvex) · 2026-10-13 · 31 قيدًا على حساب QNB Suspense 100103</t>
+          <t>إعداد: التدقيق الداخلي (Solvex) · 2026-10-13 · 31 قيدًا على QNB Suspense 100103 · (قيد 0103/8,000 تمّ فكّه كنموذج)</t>
         </is>
       </c>
     </row>
@@ -534,35 +554,30 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>التاريخ</t>
+          <t>المبلغ (ر.ق)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>المبلغ</t>
+          <t>الطرف المدين</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>مدين (حساب/مبلغ)</t>
+          <t>الطرف الدائن</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>دائن (حساب/مبلغ)</t>
+          <t>البيان</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>البيان</t>
+          <t>التصنيف</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>التصنيف</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>المعالجة</t>
         </is>
@@ -571,38 +586,33 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0072</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
+          <t>0072</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
         <v>9000</v>
       </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>502006 · إيجار المحلات</t>
+        </is>
+      </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>502006 إيجار المحلات - Shops Rent = 9,000</t>
+          <t>100103 · QNB معلّق</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 9,000</t>
+          <t>REGULAR CLEARING 00000314 - إيجار محلات</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>REGULAR CLEARING 00000314 - إيجار محلات</t>
+          <t>إعادة تصنيف مصروف</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>إعادة تصنيف مصروف</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>إعادة تصنيف — تأكيد المرفق</t>
         </is>
@@ -611,38 +621,33 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0073</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
+          <t>0073</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
         <v>9781</v>
       </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>502006 · إيجار المحلات</t>
+        </is>
+      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>502006 إيجار المحلات - Shops Rent = 9,781</t>
+          <t>100103 · QNB معلّق</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 9,781</t>
+          <t>REGULAR CLEARING 00000277 - إيجار محلات</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>REGULAR CLEARING 00000277 - إيجار محلات</t>
+          <t>إعادة تصنيف مصروف</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>إعادة تصنيف مصروف</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>إعادة تصنيف — تأكيد المرفق</t>
         </is>
@@ -651,38 +656,33 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0074</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
+          <t>0074</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
         <v>9000</v>
       </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>502006 · إيجار المحلات</t>
+        </is>
+      </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>502006 إيجار المحلات - Shops Rent = 9,000</t>
+          <t>100103 · QNB معلّق</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 9,000</t>
+          <t>REGULAR CLEARING 00000315 - إيجار محلات (شيك 315 حصّل)</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>REGULAR CLEARING 00000315 - إيجار محلات (شيك 315 حصّل)</t>
+          <t>إعادة تصنيف مصروف</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>إعادة تصنيف مصروف</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>إعادة تصنيف — تأكيد المرفق</t>
         </is>
@@ -691,38 +691,33 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0075</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
+          <t>0075</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
         <v>400</v>
       </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>502005 · رسوم بنكية</t>
+        </is>
+      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>502005 المصاريف والرسوم البنكية العامة - Bank Charges &amp; Fees (General) = 400</t>
+          <t>100103 · QNB معلّق</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 400</t>
+          <t>رسوم شيك مرتجع 004</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>رسوم شيك مرتجع 004</t>
+          <t>إعادة تصنيف مصروف</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>إعادة تصنيف مصروف</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>إعادة تصنيف — تأكيد المرفق</t>
         </is>
@@ -731,38 +726,33 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0078</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
+          <t>0078</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
         <v>2000</v>
       </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>101021 · طرف علاقة — أعلاف</t>
+        </is>
+      </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>101021 Related Party Company Alamrwa Feed = 2,000</t>
+          <t>100103 · QNB معلّق</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 2,000</t>
+          <t>REGULAR CLEARING 00000083 - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>REGULAR CLEARING 00000083 - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -771,38 +761,33 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0079</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n">
+          <t>0079</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
         <v>3000</v>
       </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>101021 · طرف علاقة — أعلاف</t>
+        </is>
+      </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>101021 Related Party Company Alamrwa Feed = 3,000</t>
+          <t>100103 · QNB معلّق</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 3,000</t>
+          <t>REGULAR CLEARING 00000071 - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>REGULAR CLEARING 00000071 - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -811,38 +796,33 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0080</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="n">
+          <t>0080</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
         <v>5000</v>
       </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>100103 · QNB معلّق</t>
+        </is>
+      </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 5,000</t>
+          <t>101021 · طرف علاقة — أعلاف</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>101021 Related Party Company Alamrwa Feed = 5,000</t>
+          <t>ATM Cash Deposit - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>ATM Cash Deposit - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -851,38 +831,33 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0081</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n">
+          <t>0081</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
         <v>3000</v>
       </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>101021 · طرف علاقة — أعلاف</t>
+        </is>
+      </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>101021 Related Party Company Alamrwa Feed = 3,000</t>
+          <t>100103 · QNB معلّق</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 3,000</t>
+          <t>REGULAR CLEARING 00000072 - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>REGULAR CLEARING 00000072 - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -891,38 +866,33 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0082</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="n">
+          <t>0082</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
         <v>2000</v>
       </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>101021 · طرف علاقة — أعلاف</t>
+        </is>
+      </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>101021 Related Party Company Alamrwa Feed = 2,000</t>
+          <t>100103 · QNB معلّق</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 2,000</t>
+          <t>REGULAR CLEARING 00000084 - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>REGULAR CLEARING 00000084 - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -931,38 +901,33 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0083</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
         <v>8000</v>
       </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>100103 · QNB معلّق</t>
+        </is>
+      </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 8,000</t>
+          <t>101019 · طرف علاقة — كافيتيريا</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>101019 Related Party Company Cafeteria- Toys = 8,000</t>
+          <t>Cash Deposit - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Cash Deposit - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -971,38 +936,33 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0084</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="n">
+          <t>0084</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
         <v>4000</v>
       </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>100103 · QNB معلّق</t>
+        </is>
+      </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 4,000</t>
+          <t>101019 · طرف علاقة — كافيتيريا</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>101019 Related Party Company Cafeteria- Toys = 4,000</t>
+          <t>Cash Deposit - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Cash Deposit - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -1011,38 +971,33 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0085</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
+          <t>0085</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
         <v>5000</v>
       </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>100103 · QNB معلّق</t>
+        </is>
+      </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 5,000</t>
+          <t>101019 · طرف علاقة — كافيتيريا</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>101019 Related Party Company Cafeteria- Toys = 5,000</t>
+          <t>Cash Deposit - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Cash Deposit - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -1051,38 +1006,33 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0086</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="n">
+          <t>0086</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
         <v>8000</v>
       </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>100101 · تحويلات نقدية</t>
+        </is>
+      </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>100101 تحويلات نقدية - Liquidity Transfer = 8,000</t>
+          <t>100103 · QNB معلّق</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 8,000</t>
+          <t>FUND TRANSFER to 008 - تحويل داخلي</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>FUND TRANSFER to 008 - تحويل داخلي</t>
+          <t>تحويل داخلي (عبر Liquidity)</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>تحويل داخلي (عبر Liquidity)</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>plug يُفكّ → مطابقة طرفي البنك مباشرة</t>
         </is>
@@ -1091,38 +1041,33 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0087</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="n">
+          <t>0087</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
         <v>13500</v>
       </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>100101 · تحويلات نقدية</t>
+        </is>
+      </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>100101 تحويلات نقدية - Liquidity Transfer = 13,500</t>
+          <t>100103 · QNB معلّق</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 13,500</t>
+          <t>FUND TRANSFER to 007 salary - تحويل داخلي</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>FUND TRANSFER to 007 salary - تحويل داخلي</t>
+          <t>تحويل داخلي (عبر Liquidity)</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>تحويل داخلي (عبر Liquidity)</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>plug يُفكّ → مطابقة طرفي البنك مباشرة</t>
         </is>
@@ -1131,38 +1076,33 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0088</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="n">
+          <t>0088</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
         <v>938.1</v>
       </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>100103 · QNB معلّق</t>
+        </is>
+      </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 938</t>
+          <t>101022 · طرف علاقة — موبايل</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>101022 Related Party company Al Marwa mobile shop Rayyan = 938</t>
+          <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Pay Later - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -1171,38 +1111,33 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0089</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n">
+          <t>0089</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
         <v>3570.1</v>
       </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>100103 · QNB معلّق</t>
+        </is>
+      </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 3,570</t>
+          <t>101022 · طرف علاقة — موبايل</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>101022 Related Party company Al Marwa mobile shop Rayyan = 3,570</t>
+          <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Pay Later - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -1211,38 +1146,33 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0090</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n">
+          <t>0090</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
         <v>4698.1</v>
       </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>100103 · QNB معلّق</t>
+        </is>
+      </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 4,698</t>
+          <t>101022 · طرف علاقة — موبايل</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>101022 Related Party company Al Marwa mobile shop Rayyan = 4,698</t>
+          <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Pay Later - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -1251,38 +1181,33 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0091</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n">
+          <t>0091</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
         <v>4322.1</v>
       </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>100103 · QNB معلّق</t>
+        </is>
+      </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 4,322</t>
+          <t>101022 · طرف علاقة — موبايل</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>101022 Related Party company Al Marwa mobile shop Rayyan = 4,322</t>
+          <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>Pay Later - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -1291,38 +1216,33 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0092</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n">
+          <t>0092</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
         <v>3288.1</v>
       </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>100103 · QNB معلّق</t>
+        </is>
+      </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 3,288</t>
+          <t>101022 · طرف علاقة — موبايل</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>101022 Related Party company Al Marwa mobile shop Rayyan = 3,288</t>
+          <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Pay Later - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -1331,38 +1251,33 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0093</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n">
+          <t>0093</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
         <v>3758.1</v>
       </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>100103 · QNB معلّق</t>
+        </is>
+      </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 3,758</t>
+          <t>101022 · طرف علاقة — موبايل</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>101022 Related Party company Al Marwa mobile shop Rayyan = 3,758</t>
+          <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Pay Later - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -1371,38 +1286,33 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0094</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n">
+          <t>0094</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
         <v>8174.2</v>
       </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>100103 · QNB معلّق</t>
+        </is>
+      </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 8,174</t>
+          <t>101022 · طرف علاقة — موبايل</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>101022 Related Party company Al Marwa mobile shop Rayyan = 8,174</t>
+          <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>Pay Later - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -1411,38 +1321,33 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0095</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n">
+          <t>0095</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
         <v>9022.1</v>
       </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>100103 · QNB معلّق</t>
+        </is>
+      </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 9,022</t>
+          <t>101022 · طرف علاقة — موبايل</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>101022 Related Party company Al Marwa mobile shop Rayyan = 9,022</t>
+          <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Pay Later - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -1451,38 +1356,33 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0096</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="n">
+          <t>0096</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
         <v>6576.2</v>
       </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>100103 · QNB معلّق</t>
+        </is>
+      </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 6,576</t>
+          <t>101022 · طرف علاقة — موبايل</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>101022 Related Party company Al Marwa mobile shop Rayyan = 6,576</t>
+          <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Pay Later - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -1491,38 +1391,33 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0097</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n">
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
         <v>8858.5</v>
       </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>100103 · QNB معلّق</t>
+        </is>
+      </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 8,858</t>
+          <t>101022 · طرف علاقة — موبايل</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>101022 Related Party company Al Marwa mobile shop Rayyan = 8,858</t>
+          <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>Pay Later - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -1531,38 +1426,33 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0098</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="n">
+          <t>0098</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
         <v>12382</v>
       </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>100101 · تحويلات نقدية</t>
+        </is>
+      </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>100101 تحويلات نقدية - Liquidity Transfer = 12,382</t>
+          <t>100103 · QNB معلّق</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 12,382</t>
+          <t>تحويل داخلي لحساب 007</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>تحويل داخلي لحساب 007</t>
+          <t>تحويل داخلي (عبر Liquidity)</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>تحويل داخلي (عبر Liquidity)</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>plug يُفكّ → مطابقة طرفي البنك مباشرة</t>
         </is>
@@ -1571,38 +1461,33 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0099</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="n">
+          <t>0099</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
         <v>7585</v>
       </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>100101 · تحويلات نقدية</t>
+        </is>
+      </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>100101 تحويلات نقدية - Liquidity Transfer = 7,585</t>
+          <t>100103 · QNB معلّق</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 7,585</t>
+          <t>تحويل داخلي لحساب 007</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>تحويل داخلي لحساب 007</t>
+          <t>تحويل داخلي (عبر Liquidity)</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>تحويل داخلي (عبر Liquidity)</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>plug يُفكّ → مطابقة طرفي البنك مباشرة</t>
         </is>
@@ -1611,38 +1496,33 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0100</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="n">
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
         <v>15197</v>
       </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>100101 · تحويلات نقدية</t>
+        </is>
+      </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>100101 تحويلات نقدية - Liquidity Transfer = 15,197</t>
+          <t>100103 · QNB معلّق</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 15,197</t>
+          <t>تحويل داخلي لحساب 007</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>تحويل داخلي لحساب 007</t>
+          <t>تحويل داخلي (عبر Liquidity)</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>تحويل داخلي (عبر Liquidity)</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>plug يُفكّ → مطابقة طرفي البنك مباشرة</t>
         </is>
@@ -1651,38 +1531,33 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0101</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n">
+          <t>0101</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n">
         <v>15000</v>
       </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>101022 · طرف علاقة — موبايل</t>
+        </is>
+      </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>101022 Related Party company Al Marwa mobile shop Rayyan = 15,000</t>
+          <t>100103 · QNB معلّق</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 15,000</t>
+          <t>مقاصّة - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>مقاصّة - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="inlineStr">
         <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
@@ -1691,118 +1566,103 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0102</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="n">
+          <t>0102</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
         <v>15000</v>
       </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>101022 · طرف علاقة — موبايل</t>
+        </is>
+      </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>101022 Related Party company Al Marwa mobile shop Rayyan = 15,000</t>
+          <t>100103 · QNB معلّق</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 15,000</t>
+          <t>مقاصّة - طرف ذي علاقة</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>مقاصّة - طرف ذي علاقة</t>
+          <t>تسوية طرف ذي علاقة</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>تسوية طرف ذي علاقة</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
           <t>مطابقة موقّعة ومختومة من الطرف</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>MISC/2026/10/0103</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="n">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>0103</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="n">
         <v>8000</v>
       </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>100103 QNB Bank Suspense = 8,000</t>
-        </is>
-      </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>100101 تحويلات نقدية - Liquidity Transfer = 8,000</t>
-        </is>
-      </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>100103 · QNB معلّق</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>100101 · تحويلات نقدية</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
         <is>
           <t>تحويل داخلي من حساب 012</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="F34" s="15" t="inlineStr">
         <is>
           <t>تحويل داخلي (عبر Liquidity)</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>plug يُفكّ → مطابقة طرفي البنك مباشرة</t>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>✓ تمّ الفكّ — المحاسب يطابق الطرفين</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>MISC/2026/10/0104</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="n">
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="n">
         <v>450</v>
       </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>100101 · تحويلات نقدية</t>
+        </is>
+      </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>100101 تحويلات نقدية - Liquidity Transfer = 450</t>
+          <t>100103 · QNB معلّق</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>100103 QNB Bank Suspense = 450</t>
+          <t>تحويل داخلي لحساب 007</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>تحويل داخلي لحساب 007</t>
+          <t>تحويل داخلي (عبر Liquidity)</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>تحويل داخلي (عبر Liquidity)</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>plug يُفكّ → مطابقة طرفي البنك مباشرة</t>
         </is>
@@ -1810,8 +1670,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
